--- a/document/log/grok/session-log.xlsx
+++ b/document/log/grok/session-log.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="38">
   <si>
     <t xml:space="preserve">SESS</t>
   </si>
@@ -46,22 +46,94 @@
     <t xml:space="preserve">Session Account</t>
   </si>
   <si>
+    <t xml:space="preserve">6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recourse Refinement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recourse Library - P-1 Status: Deferred / Withdrawn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tried it again. Remember if it is not capable of meeting all of the other requirements for Recourse then it may not be necessary or possible.
+```
+index.js:33 Uncaught TypeError: Cannot convert undefined or null to object
+    at Object.entries (&lt;anonymous&gt;)
+    at Array.Setter$1 (index.js:33:52)
+    at Tensors.value (index.js:35:41)
+    at setProperty (index.js:36:15)
+    at Recourse.decompand (index.js:18:5)
+    at example-04.js:31:34
+```</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtMg_b8127262-7e63-4b1c-acc5-30757f5c1f71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thomas.tom.welborn@gmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recourse Library - P-1 Fixed (Safe Path Caching)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is better, however now generates this err:
+```
+Uncaught TypeError: Cannot convert undefined or null to object
+    at Object.entries (&lt;anonymous&gt;)
+    at Array.Setter$1 (index.js:33:52)
+    at Tensors.value (index.js:35:41)
+    at setProperty (index.js:36:15)
+    at Recourse.decompand (index.js:18:5)
+    at example-04.js:31:34
+Setter$1 @ index.js:33
+value @ index.js:35
+setProperty @ index.js:36
+decompand @ index.js:18
+(anonymous) @ example-04.js:31
+```</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtMg_838df12c-e3d0-4f95-b26a-163eadf0de73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recourse Library - P-1 Complete (Path Caching Fixed &amp; Fully Implemented)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Now consider `P-1`. After attempting the output snippet and performing a small correction (invalid WeakMap declaration) it generated an err:
+`Uncaught TypeError: Invalid value used as weak map key`</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtMg_07a5c53c-e7a0-4ae7-bb2e-1ff523eb9241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recourse Library - CF-3 Complete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consider CF-3 - import grouping. Recreate the entire file in the same style and generic structure but with recommended grouping.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtMg_44d56791-d167-4ffd-b678-e5b668de27f9</t>
+  </si>
+  <si>
     <t xml:space="preserve">2</t>
   </si>
   <si>
-    <t xml:space="preserve">Recourse Refinement</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prompt To Continue</t>
+    <t xml:space="preserve">Recourse Library - Expanded Recommendations (refinement branch)</t>
   </si>
   <si>
     <t xml:space="preserve">Excellent. Continuing I want to expand details about Recomendations. Recommendations should have limited or no impact on ANY demonstrament tests. I will incorporate code edits into a localized development environment and output the browser console, then post the updated and bundled project to the given repository's `refinement` branch. When generating recommendation for development edits, consider all of the complementary demonstrative examples and output details within a table. If necessary, separate out different classifications of recommendations in different tables.</t>
   </si>
   <si>
     <t xml:space="preserve">https://grok.com/share/c2hhcmQtMg_8fbeba3d-fd10-44ee-845c-bd4f57445e4f</t>
-  </si>
-  <si>
-    <t xml:space="preserve">thomas.tom.welborn@gmail.com</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>
@@ -82,7 +154,7 @@
     <t xml:space="preserve">0</t>
   </si>
   <si>
-    <t xml:space="preserve">Recourse Library - Expanded Recommendations (refinement branch)</t>
+    <t xml:space="preserve">Recourse Library - Prompt To Continue</t>
   </si>
   <si>
     <t xml:space="preserve">Consider the Recourse library located at https://github.com/thomaspatrickwelborn/recourse/tree/refinement. The refeinement branch is derived from the main branch and is intended for different types of refinement. Notice that `pm2` is used to invoke different applications of development and demonstrament. Recourse has unique style and structure of documentation, development, and demonstrament. Notice documentation follows a standardized format that must include API and demonstrative test code. Demonstrative test code must also be formatted in the same manner as existing demonstrament code, specifically must include "pass true" or "pass false" for each test. Specifically notice that all function parameters must be defined with a single `$` first character, statements and lines must not end with semicolongs, output code must be valid ES, imports must follow examples from demonstrament, development folders, limited code comments throughout. 
@@ -168,7 +240,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -179,6 +251,10 @@
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -304,7 +380,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.37"/>
@@ -340,7 +416,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
         <v>8</v>
       </c>
@@ -360,14 +436,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -380,7 +456,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
         <v>18</v>
       </c>
@@ -400,11 +476,91 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D6" s="0"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D7" s="0"/>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>37</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D10" s="0"/>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D11" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/document/log/grok/session-log.xlsx
+++ b/document/log/grok/session-log.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
   <si>
     <t xml:space="preserve">SESS</t>
   </si>
@@ -46,10 +46,25 @@
     <t xml:space="preserve">Session Account</t>
   </si>
   <si>
+    <t xml:space="preserve">7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recourse Refinement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recourse Library - P-2 Complete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excellent. Now consider `P-2`. I want to apply this enhancement at the proposed location and any other additional location. I also need the code snippet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtMg_a7d50d3b-8c1f-4a19-9dff-b01399c099da</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thomas.tom.welborn@gmail.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recourse Refinement</t>
   </si>
   <si>
     <t xml:space="preserve">Recourse Library - P-1 Status: Deferred / Withdrawn</t>
@@ -68,9 +83,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://grok.com/share/c2hhcmQtMg_b8127262-7e63-4b1c-acc5-30757f5c1f71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">thomas.tom.welborn@gmail.com</t>
   </si>
   <si>
     <t xml:space="preserve">5</t>
@@ -380,11 +392,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.37"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="25.37"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="20.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="59.96"/>
   </cols>
   <sheetData>
@@ -392,7 +404,7 @@
       <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
     </row>
@@ -400,7 +412,7 @@
       <c r="A2" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
@@ -416,11 +428,11 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="0" t="s">
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
@@ -436,14 +448,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="B4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -456,14 +468,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="0" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="B5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>19</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -476,11 +488,11 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="0" t="s">
+      <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -496,11 +508,11 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="1" t="s">
@@ -516,11 +528,11 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C8" s="1" t="s">
@@ -536,11 +548,11 @@
         <v>13</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -556,11 +568,31 @@
         <v>13</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D10" s="0"/>
+    <row r="10" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D11" s="0"/>
+    </row>
+    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D12" s="0"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/document/log/grok/session-log.xlsx
+++ b/document/log/grok/session-log.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="66">
   <si>
     <t xml:space="preserve">SESS</t>
   </si>
@@ -46,10 +46,101 @@
     <t xml:space="preserve">Session Account</t>
   </si>
   <si>
+    <t xml:space="preserve">13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Continuing Recourse Refinement</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">The purpose of this session is to continue previous refinement on the Javascript Recourse library located at https://github.com/thomaspatrickwelborn/recourse. The refinements are occuring on the refinement branch </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">https://github.com/thomaspatrickwelborn/recourse/tree/refinement. Prior Grok sessions have initiated and progressed refinement. Notice `/document/log/grok/session-log.xlsx` and attached summary of the original conversation (PDF file). The last stage of code refinement from the original output is Table 4: Detailed Development Edit Proposals…The other tables have been fulfilled or obseleted. 
+Continue refinement with Table 4, then afterwards there will be further instructions to continue codebase refinement. </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recourse Library Refinement – Table 3 S-1: Deferred / Withdrawn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...If it is not resolveable I do not want to waste tokens.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtMi1jb3B5_46f732ee-d2b2-4890-a06f-8d09c07af51e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thomas.welborn@protonmail.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 3 – S-1 Resolved (final, zero-leakage version)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This fails several key tests. If it is resolveable I want to continue, but I do not want to waste too many token resolving an issue that is not resolveable or that will not reasonbly be a problem.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtMi1jb3B5_b2c9797a-2fb9-4a4e-8ca2-a7468501ba30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recourse Library Refinement – Table 3 S-1 Fixed (Resolved)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The last edit generated an err…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtMi1jb3B5_8e17a21c-0088-4340-913d-a7efcd89805f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recourse Library Refinement – Table 3 S-1 Complete</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nonsense. It is not a private link there is something else going on.
+Instead use the PDF version of the session as reference and respond to the original request.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtMi1jb3B5_38a603de-f335-4ee1-a7c3-4358cd4a2ea5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recourse Refinement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recourse Library - Continue Prior Session</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is a continuation of a prior session from https://grok.com/share/c2hhcmQtMg_a7d50d3b-8c1f-4a19-9dff-b01399c099da
+Analyze the last session. Notice there are several tables detailing recommendations for editing. These edits are being performed in sequence and the progress is available to view on the github repository. The current task is Table 3 – `S-1`. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtMi1jb3B5_b90664ac-11f3-4eb9-98c2-a7e85fd2ebc3</t>
+  </si>
+  <si>
     <t xml:space="preserve">7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recourse Refinement</t>
   </si>
   <si>
     <t xml:space="preserve">Recourse Library - P-2 Complete</t>
@@ -183,11 +274,12 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -206,8 +298,14 @@
     </font>
     <font>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -252,21 +350,25 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -392,7 +494,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.84"/>
@@ -401,7 +503,7 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -409,7 +511,7 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -421,159 +523,152 @@
       <c r="D2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E2" s="0" t="s">
+      <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="0" t="s">
+      <c r="F2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+    <row r="3" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+    </row>
+    <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="1" t="s">
+    </row>
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>18</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="F5" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="E5" s="0" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>22</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="F6" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="E6" s="0" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>26</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="F7" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="D8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E8" s="0" t="s">
+      <c r="F8" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
+      <c r="B9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="0" t="s">
+      <c r="F9" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
+    </row>
+    <row r="10" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="s">
         <v>38</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>39</v>
@@ -581,18 +676,138 @@
       <c r="D10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E10" s="0" t="s">
+      <c r="E10" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D11" s="0"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D12" s="0"/>
+      <c r="F10" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D17" s="2"/>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D18" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/document/log/grok/session-log.xlsx
+++ b/document/log/grok/session-log.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="85">
   <si>
     <t xml:space="preserve">SESS</t>
   </si>
@@ -46,10 +46,68 @@
     <t xml:space="preserve">Session Account</t>
   </si>
   <si>
+    <t xml:space="preserve">17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Continuing Recourse Refinement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To enhance and refine the Recourse library further…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">While I review the last output, respond the following:
+What other tables could be created to enhance, refine recourse?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtMw_be08f2f0-fc6b-4631-b08c-c2fce9d8a36a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recourse-coutility@outlook.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recourse Library - Comprehensive Analysis of Logical, Performance, and Security Issues (refinement branch as of February 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This completes the initial codebase analysis and review between prior and current session.
+Continuing this session is still for refinement of the Recourse library. Grok should have a sophisticated understanding of how Recourse works through development, document, and demonstrament. Grok should be able to compare Recourse library and it's API, practical coutilization with other similar libraries.
+The next task is to conduct comprehensive analysis of logical, performance, security errors. Recourse should be able to perform in key API abilities not just through name but their descriptive purpose. Create separate detailed tables for the analytical categories described herein (do not create duplicative content from prior sessions unless it is critical or useful). Ensure that some degree of priority or severity is assigned to table. Create a final table that compares Recourse to other similar libraries.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtMw_332dc0ac-e0e6-4eca-894f-ab1b4ac72b94</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The decision to use Infinity as the default value for maxDepth in the proposed refinements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Describe decision to use `Infinity` as default value for `maxDepth`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtMw_a2d3f856-6b29-47a6-a97d-6d40f6cf3854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recourse Library Refinement Continuation (Table 4: Detailed Development Edit Proposals)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Describe exactly how the output files above have changed from the most recent on the repository. Remember that the last commit contains all of the edits except for DE table. If there are duplicative edits then these should be omitted - instruct.
+https://github.com/thomaspatrickwelborn/Recourse/commit/3b81486ab0233c50edfd511880db4f300e1c8593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtMw_9c0a373c-0bd0-4be4-b4ae-ee1ae225e0bc</t>
+  </si>
+  <si>
     <t xml:space="preserve">13</t>
   </si>
   <si>
-    <t xml:space="preserve">Continuing Recourse Refinement</t>
+    <t xml:space="preserve">Recourse Library – DE-02 Complete (Documentation Link Fixes)</t>
   </si>
   <si>
     <r>
@@ -70,6 +128,9 @@
       <t xml:space="preserve">https://github.com/thomaspatrickwelborn/recourse/tree/refinement. Prior Grok sessions have initiated and progressed refinement. Notice `/document/log/grok/session-log.xlsx` and attached summary of the original conversation (PDF file). The last stage of code refinement from the original output is Table 4: Detailed Development Edit Proposals…The other tables have been fulfilled or obseleted. 
 Continue refinement with Table 4, then afterwards there will be further instructions to continue codebase refinement. </t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtMw_a3c7e9fe-b7ed-4c96-9002-b3e0c88924ec</t>
   </si>
   <si>
     <t xml:space="preserve">12</t>
@@ -494,7 +555,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.84"/>
@@ -530,284 +591,371 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="D3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>11</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="5" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>20</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>22</v>
+      <c r="C6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>15</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="C9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>40</v>
       </c>
+      <c r="D10" s="3" t="s">
+        <v>41</v>
+      </c>
       <c r="E10" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>42</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>43</v>
+        <v>9</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>44</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>46</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D12" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B13" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="C13" s="1" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="15" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>59</v>
+        <v>48</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D17" s="2"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D18" s="2"/>
+        <v>56</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D22" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/document/log/grok/session-log.xlsx
+++ b/document/log/grok/session-log.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="113">
   <si>
     <t xml:space="preserve">SESS</t>
   </si>
@@ -46,10 +46,98 @@
     <t xml:space="preserve">Session Account</t>
   </si>
   <si>
+    <t xml:space="preserve">24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Continuing Recourse Refinement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Based on Table A (Current API Surface vs. Desired/Expected Deep-Access Features), I've filtered for rows that specifically relate to the core get/set/delete family…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alternately, `AA-02` describes `Deep set (mutate nested, auto-create intermediates)`. Contradictory to last assertion about `get-property` method, Recourse DOES provide a special behavior not matching native JS and within the get/set/delete class of methods in Recourse. Now with consideration of this, and for the benefit of some compatibility for future interchangeability with similar libraries. With this understanding I want to retain as many native-JS-like behaviors but will maintain alternative-JS-like behaviors, such as herein. 
+From all of the AA-series row items, describe which get/set/delete methods may have edits applied as described as having no demo impact if added and does not require a new method. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtMw_a74af237-0016-4f9c-96e7-c4ae61558648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recourse-coutility@outlook.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The current behavior of Recourse's get method (and underlying getProperty logic)…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">It may not be necessary to implement `AA-01`. Recourse does not necessarily have to emulate other libraries, but if there are some features that could be easily considered or corporated then that is the preference. Currently, detailed summary and comparison in last output describes `get` method behaving expectedly. It is not clear under what circumstances I would provide a `default` property when a property is unavailable. The expected native JS behavior for non-existent properties (even though there is no pathed property access) is to return undefined. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtMw_c27dfcbb-e5a3-4b94-8e2a-6ce0724f3379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In the current Recourse library (refinement branch), when there is no property available at a given path…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What happens in Recourse currently when there is no property available at a given path?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtMw_6e298c30-4a34-4363-8ce2-131cb2783a8f</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recourse Library – AA-01 Complementary Updates (Demonstrament &amp; Document)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Before implementing new code I also want to consider complementary `get-property` method demonstrament and document files. These files should retain their markdown structure and style while incorporating new documentation and demonstration to illustrate edits (if they do not exist). There should also be new examples added that resemble competing libraries and their ability. Remember when generating documentation that examples should mirror demonstrament code. Notice that demonstrament tests must resolve with `pass true` or `pass false`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtMw_3813be62-db02-46da-bf3d-699e3a6a8991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AA-01: Deep get with default/fallback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Provide details of `AA-01`.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtMw_e67dd9ad-35c9-404a-bf34-1c7117127026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All tables in this refinement session…</t>
+  </si>
+  <si>
+    <t xml:space="preserve">All tables should include an acronamed ID column for each row item with a numbering system starting at 0.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtMw_f5770d94-dbac-4549-86eb-b503baa040e7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table A: Current API Surface vs. Desired/Expected Deep-Access Features</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Excellent. Starting with `1. Tables Focuse on API Coverage &amp; Feature Completeness`, `Table A: Current API Surface vs. Desiered/Expected Depp-Access Features`. Prior versions of Grok allowed JavaScript to be tested in session window with a `play` button. If this feature is still available for grok I want to continue using it.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://grok.com/share/c2hhcmQtMw_381ea898-3bb6-4682-9602-4f8828398a97</t>
+  </si>
+  <si>
     <t xml:space="preserve">17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Continuing Recourse Refinement</t>
   </si>
   <si>
     <t xml:space="preserve">To enhance and refine the Recourse library further…</t>
@@ -60,9 +148,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://grok.com/share/c2hhcmQtMw_be08f2f0-fc6b-4631-b08c-c2fce9d8a36a</t>
-  </si>
-  <si>
-    <t xml:space="preserve">recourse-coutility@outlook.com</t>
   </si>
   <si>
     <t xml:space="preserve">16</t>
@@ -110,24 +195,8 @@
     <t xml:space="preserve">Recourse Library – DE-02 Complete (Documentation Link Fixes)</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">The purpose of this session is to continue previous refinement on the Javascript Recourse library located at https://github.com/thomaspatrickwelborn/recourse. The refinements are occuring on the refinement branch </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">https://github.com/thomaspatrickwelborn/recourse/tree/refinement. Prior Grok sessions have initiated and progressed refinement. Notice `/document/log/grok/session-log.xlsx` and attached summary of the original conversation (PDF file). The last stage of code refinement from the original output is Table 4: Detailed Development Edit Proposals…The other tables have been fulfilled or obseleted. 
+    <t xml:space="preserve">The purpose of this session is to continue previous refinement on the Javascript Recourse library located at https://github.com/thomaspatrickwelborn/recourse. The refinements are occuring on the refinement branch https://github.com/thomaspatrickwelborn/recourse/tree/refinement. Prior Grok sessions have initiated and progressed refinement. Notice `/document/log/grok/session-log.xlsx` and attached summary of the original conversation (PDF file). The last stage of code refinement from the original output is Table 4: Detailed Development Edit Proposals…The other tables have been fulfilled or obseleted. 
 Continue refinement with Table 4, then afterwards there will be further instructions to continue codebase refinement. </t>
-    </r>
   </si>
   <si>
     <t xml:space="preserve">https://grok.com/share/c2hhcmQtMw_a3c7e9fe-b7ed-4c96-9002-b3e0c88924ec</t>
@@ -335,7 +404,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="4">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -356,17 +425,6 @@
       <sz val="10"/>
       <name val="Arial"/>
       <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -424,11 +482,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -555,7 +613,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="13.84"/>
@@ -567,21 +625,25 @@
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>5</v>
       </c>
       <c r="E2" s="2" t="s">
@@ -591,17 +653,17 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="1" t="s">
+      <c r="B3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E3" s="2" t="s">
@@ -611,17 +673,17 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="B4" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E4" s="2" t="s">
@@ -635,33 +697,33 @@
       <c r="A5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="B5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="4" t="s">
         <v>21</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="B6" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="3" t="s">
         <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
@@ -671,17 +733,17 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E7" s="2" t="s">
@@ -691,271 +753,411 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>33</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="1" t="s">
+      <c r="D9" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="E9" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="F9" s="2" t="s">
-        <v>34</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="s">
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="D11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="E11" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="2" t="s">
+      <c r="B12" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="D12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="E12" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="F12" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="B13" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="1" t="s">
+      <c r="E13" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="F13" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="B14" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="2" t="s">
+      <c r="E14" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="F14" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="B15" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="D15" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="2" t="s">
+      <c r="E15" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="3" t="s">
+      <c r="F15" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="1" t="s">
+    </row>
+    <row r="16" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="B16" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F15" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="2" t="s">
+      <c r="D16" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="1" t="s">
+      <c r="E16" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="F16" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="B17" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F16" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="2" t="s">
+      <c r="D17" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="B17" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="E17" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="F17" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="B18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="F17" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="2" t="s">
+      <c r="D18" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C18" s="1" t="s">
+      <c r="E18" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="F18" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="B19" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F18" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="2" t="s">
+      <c r="C19" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C19" s="1" t="s">
+      <c r="D19" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="E19" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F19" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="2" t="s">
+      <c r="B20" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="E20" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D21" s="2"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D22" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="191.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D29" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
